--- a/Modelo de dominio enriquesido.xlsx
+++ b/Modelo de dominio enriquesido.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leand\Desktop\DOO\DOO\Barberia\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/120f6d501c463b80/Escritorio/leo/Doo/Barberia proyecto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE31A87C-6058-43A7-9003-62FF9BBE7C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{DE31A87C-6058-43A7-9003-62FF9BBE7C9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{121342FC-5773-49B3-934A-2F4179CA8ED1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="566" firstSheet="18" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="566" firstSheet="14" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Modelo de Dominio" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
     <sheet name="C-Multa" sheetId="29" r:id="rId27"/>
     <sheet name="M-Multa" sheetId="30" r:id="rId28"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -360,7 +360,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="327">
   <si>
     <t>Ir a objetos de dominio &gt;&gt;&gt;&gt;</t>
   </si>
@@ -1674,7 +1674,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2016,6 +2016,15 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2024,18 +2033,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2348,12 +2345,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.109375" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -2386,7 +2383,7 @@
       <c r="AB1" s="5"/>
       <c r="AC1" s="5"/>
     </row>
-    <row r="2" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -2416,7 +2413,7 @@
       <c r="AB2" s="5"/>
       <c r="AC2" s="5"/>
     </row>
-    <row r="3" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -2447,7 +2444,7 @@
       <c r="AB3" s="5"/>
       <c r="AC3" s="5"/>
     </row>
-    <row r="4" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -2478,7 +2475,7 @@
       <c r="AB4" s="5"/>
       <c r="AC4" s="5"/>
     </row>
-    <row r="5" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -2509,7 +2506,7 @@
       <c r="AB5" s="5"/>
       <c r="AC5" s="5"/>
     </row>
-    <row r="6" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -2540,7 +2537,7 @@
       <c r="AB6" s="5"/>
       <c r="AC6" s="5"/>
     </row>
-    <row r="7" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -2571,7 +2568,7 @@
       <c r="AB7" s="5"/>
       <c r="AC7" s="5"/>
     </row>
-    <row r="8" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -2602,7 +2599,7 @@
       <c r="AB8" s="5"/>
       <c r="AC8" s="5"/>
     </row>
-    <row r="9" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -2633,7 +2630,7 @@
       <c r="AB9" s="5"/>
       <c r="AC9" s="5"/>
     </row>
-    <row r="10" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -2664,7 +2661,7 @@
       <c r="AB10" s="5"/>
       <c r="AC10" s="5"/>
     </row>
-    <row r="11" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -2695,7 +2692,7 @@
       <c r="AB11" s="5"/>
       <c r="AC11" s="5"/>
     </row>
-    <row r="12" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -2726,7 +2723,7 @@
       <c r="AB12" s="5"/>
       <c r="AC12" s="5"/>
     </row>
-    <row r="13" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -2757,7 +2754,7 @@
       <c r="AB13" s="5"/>
       <c r="AC13" s="5"/>
     </row>
-    <row r="14" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -2788,7 +2785,7 @@
       <c r="AB14" s="5"/>
       <c r="AC14" s="5"/>
     </row>
-    <row r="15" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -2819,7 +2816,7 @@
       <c r="AB15" s="5"/>
       <c r="AC15" s="5"/>
     </row>
-    <row r="16" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -2850,7 +2847,7 @@
       <c r="AB16" s="5"/>
       <c r="AC16" s="5"/>
     </row>
-    <row r="17" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -2881,7 +2878,7 @@
       <c r="AB17" s="5"/>
       <c r="AC17" s="5"/>
     </row>
-    <row r="18" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -2912,7 +2909,7 @@
       <c r="AB18" s="5"/>
       <c r="AC18" s="5"/>
     </row>
-    <row r="19" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -2943,7 +2940,7 @@
       <c r="AB19" s="5"/>
       <c r="AC19" s="5"/>
     </row>
-    <row r="20" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -2974,7 +2971,7 @@
       <c r="AB20" s="5"/>
       <c r="AC20" s="5"/>
     </row>
-    <row r="21" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -3005,7 +3002,7 @@
       <c r="AB21" s="5"/>
       <c r="AC21" s="5"/>
     </row>
-    <row r="22" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -3036,7 +3033,7 @@
       <c r="AB22" s="5"/>
       <c r="AC22" s="5"/>
     </row>
-    <row r="23" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -3067,7 +3064,7 @@
       <c r="AB23" s="5"/>
       <c r="AC23" s="5"/>
     </row>
-    <row r="24" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -3098,7 +3095,7 @@
       <c r="AB24" s="5"/>
       <c r="AC24" s="5"/>
     </row>
-    <row r="25" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -3129,7 +3126,7 @@
       <c r="AB25" s="5"/>
       <c r="AC25" s="5"/>
     </row>
-    <row r="26" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -3160,7 +3157,7 @@
       <c r="AB26" s="5"/>
       <c r="AC26" s="5"/>
     </row>
-    <row r="27" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -3191,7 +3188,7 @@
       <c r="AB27" s="5"/>
       <c r="AC27" s="5"/>
     </row>
-    <row r="28" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -3222,7 +3219,7 @@
       <c r="AB28" s="5"/>
       <c r="AC28" s="5"/>
     </row>
-    <row r="29" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -3253,7 +3250,7 @@
       <c r="AB29" s="5"/>
       <c r="AC29" s="5"/>
     </row>
-    <row r="30" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -3284,7 +3281,7 @@
       <c r="AB30" s="5"/>
       <c r="AC30" s="5"/>
     </row>
-    <row r="31" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -3315,7 +3312,7 @@
       <c r="AB31" s="5"/>
       <c r="AC31" s="5"/>
     </row>
-    <row r="32" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -3346,7 +3343,7 @@
       <c r="AB32" s="5"/>
       <c r="AC32" s="5"/>
     </row>
-    <row r="33" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -3377,7 +3374,7 @@
       <c r="AB33" s="5"/>
       <c r="AC33" s="5"/>
     </row>
-    <row r="34" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -3408,7 +3405,7 @@
       <c r="AB34" s="5"/>
       <c r="AC34" s="5"/>
     </row>
-    <row r="35" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -3439,7 +3436,7 @@
       <c r="AB35" s="5"/>
       <c r="AC35" s="5"/>
     </row>
-    <row r="36" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -3470,7 +3467,7 @@
       <c r="AB36" s="5"/>
       <c r="AC36" s="5"/>
     </row>
-    <row r="37" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -3501,7 +3498,7 @@
       <c r="AB37" s="5"/>
       <c r="AC37" s="5"/>
     </row>
-    <row r="38" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -3532,7 +3529,7 @@
       <c r="AB38" s="5"/>
       <c r="AC38" s="5"/>
     </row>
-    <row r="39" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -3563,7 +3560,7 @@
       <c r="AB39" s="5"/>
       <c r="AC39" s="5"/>
     </row>
-    <row r="40" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -3594,7 +3591,7 @@
       <c r="AB40" s="5"/>
       <c r="AC40" s="5"/>
     </row>
-    <row r="41" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -3625,7 +3622,7 @@
       <c r="AB41" s="5"/>
       <c r="AC41" s="5"/>
     </row>
-    <row r="42" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -3656,7 +3653,7 @@
       <c r="AB42" s="5"/>
       <c r="AC42" s="5"/>
     </row>
-    <row r="43" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -3687,7 +3684,7 @@
       <c r="AB43" s="5"/>
       <c r="AC43" s="5"/>
     </row>
-    <row r="44" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -3718,7 +3715,7 @@
       <c r="AB44" s="5"/>
       <c r="AC44" s="5"/>
     </row>
-    <row r="45" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -3749,7 +3746,7 @@
       <c r="AB45" s="5"/>
       <c r="AC45" s="5"/>
     </row>
-    <row r="46" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -3780,7 +3777,7 @@
       <c r="AB46" s="5"/>
       <c r="AC46" s="5"/>
     </row>
-    <row r="47" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -3811,7 +3808,7 @@
       <c r="AB47" s="5"/>
       <c r="AC47" s="5"/>
     </row>
-    <row r="48" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -3842,7 +3839,7 @@
       <c r="AB48" s="5"/>
       <c r="AC48" s="5"/>
     </row>
-    <row r="49" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -3873,7 +3870,7 @@
       <c r="AB49" s="5"/>
       <c r="AC49" s="5"/>
     </row>
-    <row r="50" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -3904,7 +3901,7 @@
       <c r="AB50" s="5"/>
       <c r="AC50" s="5"/>
     </row>
-    <row r="51" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -3935,7 +3932,7 @@
       <c r="AB51" s="5"/>
       <c r="AC51" s="5"/>
     </row>
-    <row r="52" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -3966,7 +3963,7 @@
       <c r="AB52" s="5"/>
       <c r="AC52" s="5"/>
     </row>
-    <row r="53" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -3997,7 +3994,7 @@
       <c r="AB53" s="5"/>
       <c r="AC53" s="5"/>
     </row>
-    <row r="54" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -4028,7 +4025,7 @@
       <c r="AB54" s="5"/>
       <c r="AC54" s="5"/>
     </row>
-    <row r="55" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -4059,7 +4056,7 @@
       <c r="AB55" s="5"/>
       <c r="AC55" s="5"/>
     </row>
-    <row r="56" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -4090,7 +4087,7 @@
       <c r="AB56" s="5"/>
       <c r="AC56" s="5"/>
     </row>
-    <row r="57" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -4121,7 +4118,7 @@
       <c r="AB57" s="5"/>
       <c r="AC57" s="5"/>
     </row>
-    <row r="58" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -4165,19 +4162,19 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
-    <col min="3" max="3" width="23.5546875" customWidth="1"/>
-    <col min="4" max="4" width="24.33203125" customWidth="1"/>
-    <col min="5" max="5" width="26.109375" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" customWidth="1"/>
+    <col min="5" max="5" width="26.140625" customWidth="1"/>
     <col min="6" max="6" width="29" customWidth="1"/>
-    <col min="7" max="9" width="26.44140625" customWidth="1"/>
-    <col min="10" max="10" width="40.44140625" customWidth="1"/>
+    <col min="7" max="9" width="26.42578125" customWidth="1"/>
+    <col min="10" max="10" width="40.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
         <v>1</v>
       </c>
@@ -4193,7 +4190,7 @@
       <c r="I1" s="26"/>
       <c r="J1" s="26"/>
     </row>
-    <row r="2" spans="1:10" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>65</v>
       </c>
@@ -4225,7 +4222,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>67</v>
       </c>
@@ -4257,7 +4254,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -4286,7 +4283,7 @@
         <v>Juan--Gómez--+57-3234528921</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26">
         <v>2</v>
       </c>
@@ -4319,7 +4316,7 @@
         <v>Jose-Miguel-Ramirez-Perez-+57-3161657782</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26">
         <v>3</v>
       </c>
@@ -4350,7 +4347,7 @@
         <v>Simon--Ochoa-Ramirez-+57-3119884321</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26">
         <v>4</v>
       </c>
@@ -4379,7 +4376,7 @@
         <v>Alexis--Gallego--+58-4127359182</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26">
         <v>5</v>
       </c>
@@ -4412,34 +4409,34 @@
         <v>Kevin-Andrés-Muñoz-Salazar-+57-3005544332</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="35"/>
     </row>
-    <row r="14" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="34"/>
       <c r="B14" s="35" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="36"/>
       <c r="B15" s="35" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="37"/>
       <c r="B16" s="35" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="46"/>
       <c r="B17" s="35" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="47"/>
       <c r="B18" s="35" t="s">
         <v>86</v>
@@ -4458,31 +4455,31 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:U14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="33.33203125" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" customWidth="1"/>
-    <col min="6" max="6" width="25.44140625" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" customWidth="1"/>
-    <col min="11" max="11" width="20.33203125" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" customWidth="1"/>
-    <col min="13" max="13" width="26.6640625" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" customWidth="1"/>
+    <col min="13" max="13" width="26.7109375" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="29.7109375" customWidth="1"/>
     <col min="16" max="16" width="27" customWidth="1"/>
-    <col min="17" max="17" width="41.44140625" customWidth="1"/>
-    <col min="18" max="18" width="38.88671875" customWidth="1"/>
-    <col min="19" max="19" width="22.88671875" customWidth="1"/>
-    <col min="20" max="20" width="25.88671875" customWidth="1"/>
+    <col min="17" max="17" width="41.42578125" customWidth="1"/>
+    <col min="18" max="18" width="38.85546875" customWidth="1"/>
+    <col min="19" max="19" width="22.85546875" customWidth="1"/>
+    <col min="20" max="20" width="25.85546875" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -4490,7 +4487,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>28</v>
       </c>
@@ -4555,7 +4552,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>'M-HorarioBarberia'!A3</f>
         <v>id</v>
@@ -4602,7 +4599,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="str">
         <f>'M-HorarioBarberia'!B3</f>
         <v>dueño</v>
@@ -4614,7 +4611,7 @@
       <c r="C4" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="132" t="s">
+      <c r="D4" s="128" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="14" t="s">
@@ -4651,7 +4648,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="100.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="str">
         <f>'M-HorarioBarberia'!C3</f>
         <v>diaDeLaSemana</v>
@@ -4704,7 +4701,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="str">
         <f>'M-HorarioBarberia'!D3</f>
         <v>horaApertura</v>
@@ -4755,7 +4752,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="str">
         <f>'M-HorarioBarberia'!E3</f>
         <v>horaCierre</v>
@@ -4801,14 +4798,14 @@
       <c r="S7" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="T7" s="130" t="s">
+      <c r="T7" s="127" t="s">
         <v>158</v>
       </c>
       <c r="U7" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -4831,7 +4828,7 @@
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
     </row>
-    <row r="9" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>62</v>
       </c>
@@ -4860,12 +4857,12 @@
       <c r="T9" s="38"/>
       <c r="U9" s="38"/>
     </row>
-    <row r="10" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="127" t="str">
+    <row r="10" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="130" t="str">
         <f>'M-HorarioBarberia'!F3</f>
         <v>Combinación única</v>
       </c>
-      <c r="B10" s="128" t="str">
+      <c r="B10" s="131" t="str">
         <f>'M-HorarioBarberia'!F2</f>
         <v>Combinacion única que indica que no puede existir más de un horario con la misma barberia, dia de la semana, hora de apertura y cierre</v>
       </c>
@@ -4892,9 +4889,9 @@
       <c r="T10" s="5"/>
       <c r="U10" s="5"/>
     </row>
-    <row r="11" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="127"/>
-      <c r="B11" s="127"/>
+    <row r="11" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130"/>
       <c r="C11" s="39" t="str">
         <f>A6</f>
         <v>horaApertura</v>
@@ -4918,9 +4915,9 @@
       <c r="T11" s="5"/>
       <c r="U11" s="5"/>
     </row>
-    <row r="12" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="127"/>
-      <c r="B12" s="127"/>
+    <row r="12" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="130"/>
+      <c r="B12" s="130"/>
       <c r="C12" s="39" t="str">
         <f>A7</f>
         <v>horaCierre</v>
@@ -4944,7 +4941,7 @@
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
     </row>
-    <row r="13" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="117"/>
@@ -4967,7 +4964,7 @@
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
     </row>
-    <row r="14" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="117"/>
@@ -5007,18 +5004,18 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="39.88671875" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="39.85546875" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="21.5546875" customWidth="1"/>
+    <col min="5" max="5" width="21.5703125" customWidth="1"/>
     <col min="6" max="6" width="43" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -5026,7 +5023,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="48" t="s">
         <v>65</v>
       </c>
@@ -5046,7 +5043,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>67</v>
       </c>
@@ -5066,7 +5063,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -5088,7 +5085,7 @@
         <v>Lunes-09:00-19:00</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26">
         <v>2</v>
       </c>
@@ -5110,7 +5107,7 @@
         <v>Martes-09:00-19:00</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26">
         <v>3</v>
       </c>
@@ -5132,7 +5129,7 @@
         <v>Miércoles-09:00-19:00</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26">
         <v>4</v>
       </c>
@@ -5154,7 +5151,7 @@
         <v>Jueves-09:00-19:00</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26">
         <v>5</v>
       </c>
@@ -5176,7 +5173,7 @@
         <v>Viernes-09:00-19:00</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26">
         <v>6</v>
       </c>
@@ -5198,7 +5195,7 @@
         <v>Sábado-08:00-21:00</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26">
         <v>7</v>
       </c>
@@ -5220,51 +5217,39 @@
         <v>Festivo-10:00-15:00</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="34"/>
       <c r="B16" s="35" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="36"/>
       <c r="B17" s="35" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="57"/>
       <c r="B18" s="35" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="37"/>
       <c r="B19" s="35" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="58"/>
       <c r="B20" s="35" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="46"/>
+    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="47"/>
       <c r="B21" s="35" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="59"/>
-      <c r="B22" s="35" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="47"/>
-      <c r="B23" s="35" t="s">
         <v>86</v>
       </c>
     </row>
@@ -5289,31 +5274,31 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:U10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="33.33203125" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" customWidth="1"/>
-    <col min="6" max="6" width="25.44140625" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" customWidth="1"/>
-    <col min="9" max="9" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" customWidth="1"/>
-    <col min="11" max="11" width="20.33203125" customWidth="1"/>
-    <col min="12" max="12" width="20.5546875" customWidth="1"/>
-    <col min="13" max="13" width="26.6640625" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" customWidth="1"/>
+    <col min="12" max="12" width="20.5703125" customWidth="1"/>
+    <col min="13" max="13" width="26.7109375" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="29.7109375" customWidth="1"/>
     <col min="16" max="16" width="27" customWidth="1"/>
-    <col min="17" max="17" width="41.44140625" customWidth="1"/>
-    <col min="18" max="18" width="38.88671875" customWidth="1"/>
-    <col min="19" max="19" width="22.88671875" customWidth="1"/>
-    <col min="20" max="20" width="25.88671875" customWidth="1"/>
+    <col min="17" max="17" width="41.42578125" customWidth="1"/>
+    <col min="18" max="18" width="38.85546875" customWidth="1"/>
+    <col min="19" max="19" width="22.85546875" customWidth="1"/>
+    <col min="20" max="20" width="25.85546875" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -5321,7 +5306,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>28</v>
       </c>
@@ -5386,7 +5371,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>'M-Regla'!A3</f>
         <v>id</v>
@@ -5433,7 +5418,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="str">
         <f>'M-Regla'!B3</f>
         <v>dueño</v>
@@ -5445,7 +5430,7 @@
       <c r="C4" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="132" t="s">
+      <c r="D4" s="128" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="14" t="s">
@@ -5482,7 +5467,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="str">
         <f>'M-Regla'!C3</f>
         <v>toleranciaTardanzaCliente</v>
@@ -5531,7 +5516,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="str">
         <f>'M-Regla'!D3</f>
         <v>montoMultaTardanzaCliente</v>
@@ -5582,7 +5567,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="str">
         <f>'M-Regla'!E3</f>
         <v>numeroMultasMaxima</v>
@@ -5631,7 +5616,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="str">
         <f>'M-Regla'!F3</f>
         <v>toleranciaTardanzaBarbero</v>
@@ -5680,7 +5665,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="str">
         <f>'M-Regla'!G3</f>
         <v>porcentajeDescuentoCita</v>
@@ -5733,7 +5718,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -5770,17 +5755,17 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="34.33203125" customWidth="1"/>
-    <col min="4" max="4" width="34.109375" customWidth="1"/>
-    <col min="5" max="5" width="32.5546875" customWidth="1"/>
+    <col min="3" max="3" width="34.28515625" customWidth="1"/>
+    <col min="4" max="4" width="34.140625" customWidth="1"/>
+    <col min="5" max="5" width="32.5703125" customWidth="1"/>
     <col min="6" max="6" width="25" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
+    <col min="7" max="7" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -5788,7 +5773,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>65</v>
       </c>
@@ -5811,7 +5796,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>67</v>
       </c>
@@ -5834,7 +5819,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -5858,25 +5843,25 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34"/>
       <c r="B9" s="35" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="36"/>
       <c r="B10" s="35" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="57"/>
       <c r="B11" s="35" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="63"/>
       <c r="B12" s="35" t="s">
         <v>83</v>
@@ -5897,31 +5882,31 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:U11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="33.33203125" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" customWidth="1"/>
-    <col min="6" max="6" width="25.44140625" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" customWidth="1"/>
-    <col min="11" max="11" width="20.33203125" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" customWidth="1"/>
-    <col min="13" max="13" width="26.6640625" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" customWidth="1"/>
+    <col min="13" max="13" width="26.7109375" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="29.7109375" customWidth="1"/>
     <col min="16" max="16" width="27" customWidth="1"/>
-    <col min="17" max="17" width="41.44140625" customWidth="1"/>
-    <col min="18" max="18" width="38.88671875" customWidth="1"/>
-    <col min="19" max="19" width="22.88671875" customWidth="1"/>
-    <col min="20" max="20" width="25.88671875" customWidth="1"/>
+    <col min="17" max="17" width="41.42578125" customWidth="1"/>
+    <col min="18" max="18" width="38.85546875" customWidth="1"/>
+    <col min="19" max="19" width="22.85546875" customWidth="1"/>
+    <col min="20" max="20" width="25.85546875" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -5929,7 +5914,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>28</v>
       </c>
@@ -5994,7 +5979,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>'M-Servicio'!A3</f>
         <v>id</v>
@@ -6041,7 +6026,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="str">
         <f>'M-Servicio'!B3</f>
         <v>dueño</v>
@@ -6053,7 +6038,7 @@
       <c r="C4" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="132" t="s">
+      <c r="D4" s="128" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="14" t="s">
@@ -6090,7 +6075,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="str">
         <f>'M-Servicio'!C3</f>
         <v>nombre</v>
@@ -6141,7 +6126,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="str">
         <f>'M-Servicio'!D3</f>
         <v>descripcion</v>
@@ -6192,7 +6177,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="str">
         <f>'M-Servicio'!E3</f>
         <v>precio</v>
@@ -6237,7 +6222,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="str">
         <f>'M-Servicio'!F3</f>
         <v>disponible</v>
@@ -6280,7 +6265,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -6303,7 +6288,7 @@
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
     </row>
-    <row r="10" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>62</v>
       </c>
@@ -6313,26 +6298,26 @@
       <c r="C10" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="131"/>
-      <c r="E10" s="131"/>
-      <c r="F10" s="131"/>
-      <c r="G10" s="131"/>
-      <c r="H10" s="131"/>
-      <c r="I10" s="131"/>
-      <c r="J10" s="131"/>
-      <c r="K10" s="131"/>
-      <c r="L10" s="131"/>
-      <c r="M10" s="131"/>
-      <c r="N10" s="131"/>
-      <c r="O10" s="131"/>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
-      <c r="R10" s="131"/>
-      <c r="S10" s="131"/>
-      <c r="T10" s="131"/>
-      <c r="U10" s="131"/>
-    </row>
-    <row r="11" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="38"/>
+      <c r="O10" s="38"/>
+      <c r="P10" s="38"/>
+      <c r="Q10" s="38"/>
+      <c r="R10" s="38"/>
+      <c r="S10" s="38"/>
+      <c r="T10" s="38"/>
+      <c r="U10" s="38"/>
+    </row>
+    <row r="11" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="str">
         <f>'M-Servicio'!G3</f>
         <v xml:space="preserve">Combinacion única </v>
@@ -6378,16 +6363,16 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="26.109375" customWidth="1"/>
-    <col min="4" max="4" width="51.88671875" customWidth="1"/>
-    <col min="5" max="6" width="22.88671875" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" customWidth="1"/>
+    <col min="4" max="4" width="51.85546875" customWidth="1"/>
+    <col min="5" max="6" width="22.85546875" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="64" t="s">
         <v>1</v>
       </c>
@@ -6399,7 +6384,7 @@
       <c r="F1" s="65"/>
       <c r="G1" s="30"/>
     </row>
-    <row r="2" spans="1:7" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>65</v>
       </c>
@@ -6422,7 +6407,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="66" t="s">
         <v>67</v>
       </c>
@@ -6445,7 +6430,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="71">
         <v>1</v>
       </c>
@@ -6470,7 +6455,7 @@
         <v>Motilada</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="71">
         <v>2</v>
       </c>
@@ -6495,7 +6480,7 @@
         <v>Corte de barba</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="71">
         <v>3</v>
       </c>
@@ -6520,7 +6505,7 @@
         <v>Perfilada de barba</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="71">
         <v>4</v>
       </c>
@@ -6545,43 +6530,43 @@
         <v>Arreglo completo de barba con toalla caliente</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34"/>
       <c r="B13" s="35" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="36"/>
       <c r="B14" s="35" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="57"/>
       <c r="B15" s="35" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="37"/>
       <c r="B16" s="35" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="77"/>
       <c r="B17" s="35" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="59"/>
       <c r="B18" s="35" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="78"/>
       <c r="B19" s="35" t="s">
         <v>86</v>
@@ -6605,31 +6590,31 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:U11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="33.33203125" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" customWidth="1"/>
-    <col min="6" max="6" width="25.44140625" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" customWidth="1"/>
-    <col min="11" max="11" width="20.33203125" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" customWidth="1"/>
-    <col min="13" max="13" width="26.6640625" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" customWidth="1"/>
+    <col min="13" max="13" width="26.7109375" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="29.7109375" customWidth="1"/>
     <col min="16" max="16" width="27" customWidth="1"/>
-    <col min="17" max="17" width="41.44140625" customWidth="1"/>
-    <col min="18" max="18" width="38.88671875" customWidth="1"/>
-    <col min="19" max="19" width="22.88671875" customWidth="1"/>
-    <col min="20" max="20" width="25.88671875" customWidth="1"/>
+    <col min="17" max="17" width="41.42578125" customWidth="1"/>
+    <col min="18" max="18" width="38.85546875" customWidth="1"/>
+    <col min="19" max="19" width="22.85546875" customWidth="1"/>
+    <col min="20" max="20" width="25.85546875" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -6637,7 +6622,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>28</v>
       </c>
@@ -6702,7 +6687,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>'M-BarberoServicio'!A3</f>
         <v>id</v>
@@ -6749,7 +6734,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="str">
         <f>'M-BarberoServicio'!B3</f>
         <v>barbero</v>
@@ -6761,7 +6746,7 @@
       <c r="C4" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="132" t="s">
+      <c r="D4" s="128" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="14" t="s">
@@ -6798,7 +6783,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="str">
         <f>'M-BarberoServicio'!C3</f>
         <v>servicio</v>
@@ -6810,7 +6795,7 @@
       <c r="C5" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="132" t="s">
+      <c r="D5" s="128" t="s">
         <v>17</v>
       </c>
       <c r="E5" s="14" t="s">
@@ -6847,7 +6832,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="str">
         <f>'M-BarberoServicio'!D3</f>
         <v>duracionServicio</v>
@@ -6898,7 +6883,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="100.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="str">
         <f>'M-BarberoServicio'!E3</f>
         <v>tiempoExtra</v>
@@ -6947,7 +6932,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
@@ -6970,7 +6955,7 @@
       <c r="T8" s="5"/>
       <c r="U8" s="5"/>
     </row>
-    <row r="9" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>62</v>
       </c>
@@ -6980,31 +6965,31 @@
       <c r="C9" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="131"/>
-      <c r="E9" s="131"/>
-      <c r="F9" s="131"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="131"/>
-      <c r="I9" s="131"/>
-      <c r="J9" s="131"/>
-      <c r="K9" s="131"/>
-      <c r="L9" s="131"/>
-      <c r="M9" s="131"/>
-      <c r="N9" s="131"/>
-      <c r="O9" s="131"/>
-      <c r="P9" s="131"/>
-      <c r="Q9" s="131"/>
-      <c r="R9" s="131"/>
-      <c r="S9" s="131"/>
-      <c r="T9" s="131"/>
-      <c r="U9" s="131"/>
-    </row>
-    <row r="10" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="127" t="str">
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="38"/>
+      <c r="O9" s="38"/>
+      <c r="P9" s="38"/>
+      <c r="Q9" s="38"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="38"/>
+      <c r="T9" s="38"/>
+      <c r="U9" s="38"/>
+    </row>
+    <row r="10" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="130" t="str">
         <f>'M-BarberoServicio'!F3</f>
         <v>Combinación única</v>
       </c>
-      <c r="B10" s="128" t="str">
+      <c r="B10" s="131" t="str">
         <f>'M-BarberoServicio'!F2</f>
         <v>Combinación única que indica que un mismo barbero no puede aparecer dos veces ofreciendo el mismo servicio</v>
       </c>
@@ -7031,9 +7016,9 @@
       <c r="T10" s="5"/>
       <c r="U10" s="5"/>
     </row>
-    <row r="11" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="127"/>
-      <c r="B11" s="127"/>
+    <row r="11" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="130"/>
+      <c r="B11" s="130"/>
       <c r="C11" s="39" t="str">
         <f>A5</f>
         <v>servicio</v>
@@ -7076,15 +7061,15 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="29.88671875" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
     <col min="3" max="5" width="42" customWidth="1"/>
-    <col min="6" max="6" width="56.109375" customWidth="1"/>
+    <col min="6" max="6" width="56.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -7092,7 +7077,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>65</v>
       </c>
@@ -7112,7 +7097,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>67</v>
       </c>
@@ -7132,7 +7117,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -7155,7 +7140,7 @@
         <v>Juan García-Motilada</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26">
         <v>2</v>
       </c>
@@ -7178,7 +7163,7 @@
         <v>Juan Ortiz-Corte de barba</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26">
         <v>3</v>
       </c>
@@ -7201,7 +7186,7 @@
         <v>Carlos Arbeladez-Perfilada de barba</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26">
         <v>4</v>
       </c>
@@ -7224,7 +7209,7 @@
         <v>Andres Ramirez-Arreglo completo de barba con toalla caliente</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26">
         <v>5</v>
       </c>
@@ -7247,7 +7232,7 @@
         <v>Juan Ortiz-Motilada</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26">
         <v>6</v>
       </c>
@@ -7270,7 +7255,7 @@
         <v>Carlos Arbeladez-Corte de barba</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26">
         <v>7</v>
       </c>
@@ -7293,7 +7278,7 @@
         <v>Juan García-Perfilada de barba</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26">
         <v>8</v>
       </c>
@@ -7316,7 +7301,7 @@
         <v>Andres Ramirez-Motilada</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="26">
         <v>9</v>
       </c>
@@ -7339,46 +7324,46 @@
         <v>Juan Zambrano-Corte de barba</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="35"/>
     </row>
-    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="35"/>
     </row>
-    <row r="15" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="35"/>
     </row>
-    <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="35"/>
     </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="35"/>
     </row>
-    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="34"/>
       <c r="B18" s="35" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="36"/>
       <c r="B19" s="35" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="57"/>
       <c r="B20" s="35" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="77"/>
       <c r="B21" s="35" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="78"/>
       <c r="B22" s="35" t="s">
         <v>86</v>
@@ -7407,31 +7392,31 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:U19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="33.33203125" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" customWidth="1"/>
-    <col min="6" max="6" width="25.44140625" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" customWidth="1"/>
-    <col min="11" max="11" width="20.33203125" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" customWidth="1"/>
-    <col min="13" max="13" width="26.6640625" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" customWidth="1"/>
+    <col min="13" max="13" width="26.7109375" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="29.7109375" customWidth="1"/>
     <col min="16" max="16" width="27" customWidth="1"/>
-    <col min="17" max="17" width="41.44140625" customWidth="1"/>
-    <col min="18" max="18" width="38.88671875" customWidth="1"/>
-    <col min="19" max="19" width="22.88671875" customWidth="1"/>
-    <col min="20" max="20" width="25.88671875" customWidth="1"/>
+    <col min="17" max="17" width="41.42578125" customWidth="1"/>
+    <col min="18" max="18" width="38.85546875" customWidth="1"/>
+    <col min="19" max="19" width="22.85546875" customWidth="1"/>
+    <col min="20" max="20" width="25.85546875" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -7439,7 +7424,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>28</v>
       </c>
@@ -7504,7 +7489,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>'M-HorarioBarbero'!A3</f>
         <v>id</v>
@@ -7551,7 +7536,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="str">
         <f>'M-HorarioBarbero'!B3</f>
         <v>barbero</v>
@@ -7563,7 +7548,7 @@
       <c r="C4" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="132" t="s">
+      <c r="D4" s="128" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="14" t="s">
@@ -7600,7 +7585,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
         <v>230</v>
       </c>
@@ -7611,7 +7596,7 @@
       <c r="C5" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="132" t="s">
+      <c r="D5" s="128" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="14" t="s">
@@ -7638,7 +7623,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="114.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="114.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="str">
         <f>'M-HorarioBarbero'!D3</f>
         <v>diaDeLaSemana</v>
@@ -7691,7 +7676,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="str">
         <f>'M-HorarioBarbero'!E3</f>
         <v>horaInicio</v>
@@ -7740,7 +7725,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="129" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="str">
         <f>'M-HorarioBarbero'!F3</f>
         <v>horaFinal</v>
@@ -7782,14 +7767,14 @@
       <c r="S8" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="T8" s="133">
+      <c r="T8" s="129">
         <v>0</v>
       </c>
       <c r="U8" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="str">
         <f>'M-HorarioBarbero'!G3</f>
         <v>fechaCreacion</v>
@@ -7836,7 +7821,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="str">
         <f>'M-HorarioBarbero'!H3</f>
         <v>fechaDesactivacion</v>
@@ -7885,7 +7870,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="str">
         <f>'M-HorarioBarbero'!I3</f>
         <v>vigente</v>
@@ -7932,7 +7917,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -7955,7 +7940,7 @@
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
     </row>
-    <row r="13" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>62</v>
       </c>
@@ -7965,31 +7950,31 @@
       <c r="C13" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="131"/>
-      <c r="E13" s="131"/>
-      <c r="F13" s="131"/>
-      <c r="G13" s="131"/>
-      <c r="H13" s="131"/>
-      <c r="I13" s="131"/>
-      <c r="J13" s="131"/>
-      <c r="K13" s="131"/>
-      <c r="L13" s="131"/>
-      <c r="M13" s="131"/>
-      <c r="N13" s="131"/>
-      <c r="O13" s="131"/>
-      <c r="P13" s="131"/>
-      <c r="Q13" s="131"/>
-      <c r="R13" s="131"/>
-      <c r="S13" s="131"/>
-      <c r="T13" s="131"/>
-      <c r="U13" s="131"/>
-    </row>
-    <row r="14" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="127" t="str">
+      <c r="D13" s="38"/>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
+      <c r="J13" s="38"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="38"/>
+      <c r="M13" s="38"/>
+      <c r="N13" s="38"/>
+      <c r="O13" s="38"/>
+      <c r="P13" s="38"/>
+      <c r="Q13" s="38"/>
+      <c r="R13" s="38"/>
+      <c r="S13" s="38"/>
+      <c r="T13" s="38"/>
+      <c r="U13" s="38"/>
+    </row>
+    <row r="14" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="130" t="str">
         <f>'M-HorarioBarbero'!M3</f>
         <v>Combinación única</v>
       </c>
-      <c r="B14" s="128" t="str">
+      <c r="B14" s="131" t="str">
         <f>'M-HorarioBarbero'!M2</f>
         <v>Combinación única que indica que un barbero no puede tener más de una agenda, cada barbero organiza todo su tiempo en un único lugar</v>
       </c>
@@ -8016,9 +8001,9 @@
       <c r="T14" s="5"/>
       <c r="U14" s="5"/>
     </row>
-    <row r="15" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="127"/>
-      <c r="B15" s="127"/>
+    <row r="15" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="130"/>
+      <c r="B15" s="130"/>
       <c r="C15" s="39" t="str">
         <f t="shared" ref="C15:C19" si="0">A6</f>
         <v>diaDeLaSemana</v>
@@ -8042,9 +8027,9 @@
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
     </row>
-    <row r="16" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="127"/>
-      <c r="B16" s="127"/>
+    <row r="16" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="130"/>
+      <c r="B16" s="130"/>
       <c r="C16" s="39" t="str">
         <f t="shared" si="0"/>
         <v>horaInicio</v>
@@ -8068,9 +8053,9 @@
       <c r="T16" s="5"/>
       <c r="U16" s="5"/>
     </row>
-    <row r="17" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="127"/>
-      <c r="B17" s="127"/>
+    <row r="17" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="130"/>
+      <c r="B17" s="130"/>
       <c r="C17" s="39" t="str">
         <f t="shared" si="0"/>
         <v>horaFinal</v>
@@ -8094,9 +8079,9 @@
       <c r="T17" s="5"/>
       <c r="U17" s="5"/>
     </row>
-    <row r="18" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="127"/>
-      <c r="B18" s="127"/>
+    <row r="18" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="130"/>
+      <c r="B18" s="130"/>
       <c r="C18" s="39" t="str">
         <f t="shared" si="0"/>
         <v>fechaCreacion</v>
@@ -8120,9 +8105,9 @@
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
     </row>
-    <row r="19" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="127"/>
-      <c r="B19" s="127"/>
+    <row r="19" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="130"/>
+      <c r="B19" s="130"/>
       <c r="C19" s="39" t="str">
         <f t="shared" si="0"/>
         <v>fechaDesactivacion</v>
@@ -8165,19 +8150,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="62.88671875" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" customWidth="1"/>
+    <col min="2" max="2" width="62.85546875" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>2</v>
       </c>
@@ -8191,7 +8176,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
@@ -8205,7 +8190,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>9</v>
       </c>
@@ -8219,7 +8204,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="89.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>11</v>
       </c>
@@ -8233,7 +8218,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="89.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="89.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>13</v>
       </c>
@@ -8247,7 +8232,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>14</v>
       </c>
@@ -8261,7 +8246,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>16</v>
       </c>
@@ -8275,7 +8260,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>17</v>
       </c>
@@ -8289,7 +8274,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>21</v>
       </c>
@@ -8303,7 +8288,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>18</v>
       </c>
@@ -8317,7 +8302,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>20</v>
       </c>
@@ -8331,7 +8316,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>22</v>
       </c>
@@ -8345,7 +8330,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>23</v>
       </c>
@@ -8359,7 +8344,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>25</v>
       </c>
@@ -8373,169 +8358,169 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12"/>
       <c r="B16" s="12"/>
       <c r="C16" s="12"/>
       <c r="D16" s="12"/>
     </row>
-    <row r="17" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12"/>
       <c r="B17" s="12"/>
       <c r="C17" s="12"/>
       <c r="D17" s="12"/>
     </row>
-    <row r="18" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
     </row>
-    <row r="19" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
     </row>
-    <row r="20" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12"/>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
     </row>
-    <row r="21" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="12"/>
       <c r="B21" s="12"/>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12"/>
       <c r="B22" s="12"/>
       <c r="C22" s="12"/>
       <c r="D22" s="12"/>
     </row>
-    <row r="23" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="12"/>
       <c r="B23" s="12"/>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
     </row>
-    <row r="24" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
       <c r="D24" s="12"/>
     </row>
-    <row r="25" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
       <c r="D25" s="12"/>
     </row>
-    <row r="26" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
     </row>
-    <row r="27" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
     </row>
-    <row r="28" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
     </row>
-    <row r="29" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
     </row>
-    <row r="30" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
     </row>
-    <row r="31" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
       <c r="B31" s="12"/>
       <c r="C31" s="12"/>
       <c r="D31" s="12"/>
     </row>
-    <row r="32" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
       <c r="B32" s="12"/>
       <c r="C32" s="12"/>
       <c r="D32" s="12"/>
     </row>
-    <row r="33" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
       <c r="D33" s="12"/>
     </row>
-    <row r="34" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12"/>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
       <c r="B35" s="12"/>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
     </row>
-    <row r="36" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12"/>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="12"/>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12"/>
       <c r="B38" s="12"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
     </row>
-    <row r="39" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="12"/>
       <c r="B39" s="12"/>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
     </row>
-    <row r="40" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12"/>
       <c r="B40" s="12"/>
       <c r="C40" s="12"/>
       <c r="D40" s="12"/>
     </row>
-    <row r="41" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="12"/>
       <c r="B41" s="12"/>
       <c r="C41" s="12"/>
       <c r="D41" s="12"/>
     </row>
-    <row r="42" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12"/>
       <c r="B42" s="12"/>
       <c r="C42" s="12"/>
       <c r="D42" s="12"/>
     </row>
-    <row r="43" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="12"/>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
@@ -8566,19 +8551,19 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="3" width="32.88671875" customWidth="1"/>
-    <col min="4" max="4" width="45.44140625" customWidth="1"/>
-    <col min="5" max="5" width="23.5546875" customWidth="1"/>
+    <col min="2" max="3" width="32.85546875" customWidth="1"/>
+    <col min="4" max="4" width="45.42578125" customWidth="1"/>
+    <col min="5" max="5" width="23.5703125" customWidth="1"/>
     <col min="6" max="9" width="36" customWidth="1"/>
     <col min="10" max="10" width="31" customWidth="1"/>
-    <col min="11" max="12" width="31.21875" customWidth="1"/>
-    <col min="13" max="13" width="55.109375" customWidth="1"/>
+    <col min="11" max="12" width="31.28515625" customWidth="1"/>
+    <col min="13" max="13" width="55.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -8596,7 +8581,7 @@
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
     </row>
-    <row r="2" spans="1:13" ht="69" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="69" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>65</v>
       </c>
@@ -8637,7 +8622,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>67</v>
       </c>
@@ -8678,7 +8663,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -8722,7 +8707,7 @@
         <v>Juan-Fernando-García-Lopez-+57-3245627890-Lunes-10:00-16:00-03/05/2025-1/01/1000</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26">
         <v>2</v>
       </c>
@@ -8766,7 +8751,7 @@
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923-Martes-09:00-15:00-02/03/2025-1/01/1000</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26">
         <v>3</v>
       </c>
@@ -8810,7 +8795,7 @@
         <v>Carlos--Arbeladez--+57-3214533321-Jueves-13:00-19:00-22/12/2022-1/01/1000</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26">
         <v>4</v>
       </c>
@@ -8854,7 +8839,7 @@
         <v>Andres--Ramirez-Patiño-+91-9876543210-Sábado-08:00-14:00-15/09/2025-01/01/2026</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26">
         <v>5</v>
       </c>
@@ -8898,45 +8883,45 @@
         <v>Andres--Ramirez-Patiño-+91-9876543210-Festivo-12:00-15:00-01/02/2026-02/03/2026</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H10" s="88"/>
     </row>
-    <row r="14" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="34"/>
       <c r="B14" s="35" t="s">
         <v>80</v>
       </c>
       <c r="C14" s="35"/>
     </row>
-    <row r="15" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="36"/>
       <c r="B15" s="35" t="s">
         <v>81</v>
       </c>
       <c r="C15" s="35"/>
     </row>
-    <row r="16" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="57"/>
       <c r="B16" s="35" t="s">
         <v>172</v>
       </c>
       <c r="C16" s="35"/>
     </row>
-    <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="37"/>
       <c r="B17" s="35" t="s">
         <v>82</v>
       </c>
       <c r="C17" s="35"/>
     </row>
-    <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="58"/>
       <c r="B18" s="35" t="s">
         <v>173</v>
       </c>
       <c r="C18" s="35"/>
     </row>
-    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="47"/>
       <c r="B19" s="35" t="s">
         <v>86</v>
@@ -8962,31 +8947,31 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="A1:U13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="33.33203125" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" customWidth="1"/>
-    <col min="6" max="6" width="25.44140625" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" customWidth="1"/>
-    <col min="11" max="11" width="20.33203125" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" customWidth="1"/>
-    <col min="13" max="13" width="26.6640625" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" customWidth="1"/>
+    <col min="13" max="13" width="26.7109375" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="29.7109375" customWidth="1"/>
     <col min="16" max="16" width="27" customWidth="1"/>
-    <col min="17" max="17" width="41.44140625" customWidth="1"/>
-    <col min="18" max="18" width="38.88671875" customWidth="1"/>
-    <col min="19" max="19" width="22.88671875" customWidth="1"/>
-    <col min="20" max="20" width="25.88671875" customWidth="1"/>
+    <col min="17" max="17" width="41.42578125" customWidth="1"/>
+    <col min="18" max="18" width="38.85546875" customWidth="1"/>
+    <col min="19" max="19" width="22.85546875" customWidth="1"/>
+    <col min="20" max="20" width="25.85546875" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -8994,7 +8979,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>28</v>
       </c>
@@ -9059,7 +9044,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>'M-Bloqueo'!A3</f>
         <v>id</v>
@@ -9106,7 +9091,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="str">
         <f>'M-Bloqueo'!B3</f>
         <v>agenda</v>
@@ -9119,7 +9104,7 @@
       <c r="C4" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="132" t="s">
+      <c r="D4" s="128" t="s">
         <v>13</v>
       </c>
       <c r="E4" s="14" t="s">
@@ -9152,7 +9137,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="str">
         <f>'M-Bloqueo'!C3</f>
         <v>fechaHoraInicio</v>
@@ -9199,7 +9184,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="str">
         <f>'M-Bloqueo'!D3</f>
         <v>fechaHoraFinal</v>
@@ -9246,7 +9231,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="str">
         <f>'M-Bloqueo'!E3</f>
         <v>nombre</v>
@@ -9297,7 +9282,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="str">
         <f>'M-Bloqueo'!F3</f>
         <v>duracion</v>
@@ -9346,7 +9331,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -9369,7 +9354,7 @@
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
     </row>
-    <row r="10" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>62</v>
       </c>
@@ -9398,12 +9383,12 @@
       <c r="T10" s="38"/>
       <c r="U10" s="38"/>
     </row>
-    <row r="11" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="127" t="str">
+    <row r="11" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="130" t="str">
         <f>'M-Bloqueo'!G3</f>
         <v>Combinación única</v>
       </c>
-      <c r="B11" s="128" t="str">
+      <c r="B11" s="131" t="str">
         <f>'M-Bloqueo'!G2</f>
         <v>Combinación única que indica que una misma agenda no puede tener dos bloqueos en una misma fecha, horaInicio y horaFinal</v>
       </c>
@@ -9430,9 +9415,9 @@
       <c r="T11" s="5"/>
       <c r="U11" s="5"/>
     </row>
-    <row r="12" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="127"/>
-      <c r="B12" s="127"/>
+    <row r="12" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="130"/>
+      <c r="B12" s="130"/>
       <c r="C12" s="39" t="str">
         <f>A5</f>
         <v>fechaHoraInicio</v>
@@ -9456,9 +9441,9 @@
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
     </row>
-    <row r="13" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="127"/>
-      <c r="B13" s="127"/>
+    <row r="13" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="130"/>
+      <c r="B13" s="130"/>
       <c r="C13" s="39" t="str">
         <f>A6</f>
         <v>fechaHoraFinal</v>
@@ -9500,18 +9485,18 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="33.6640625" customWidth="1"/>
-    <col min="3" max="3" width="36.44140625" customWidth="1"/>
-    <col min="4" max="4" width="32.33203125" customWidth="1"/>
-    <col min="5" max="5" width="25.109375" customWidth="1"/>
-    <col min="6" max="6" width="25.5546875" customWidth="1"/>
-    <col min="7" max="7" width="68.109375" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" customWidth="1"/>
+    <col min="3" max="3" width="36.42578125" customWidth="1"/>
+    <col min="4" max="4" width="32.28515625" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" customWidth="1"/>
+    <col min="6" max="6" width="25.5703125" customWidth="1"/>
+    <col min="7" max="7" width="68.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -9521,7 +9506,7 @@
       <c r="C1" s="6"/>
       <c r="D1" s="6"/>
     </row>
-    <row r="2" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>65</v>
       </c>
@@ -9544,7 +9529,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>67</v>
       </c>
@@ -9567,7 +9552,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -9592,7 +9577,7 @@
         <v>Agenda de Juan García-07/09/2026 10:00-07/09/2026 12:00</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26">
         <v>2</v>
       </c>
@@ -9617,7 +9602,7 @@
         <v>Agenda de Juan Ortiz-08/09/2026 09:30-08/09/2026 11:00</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26">
         <v>3</v>
       </c>
@@ -9642,7 +9627,7 @@
         <v>Agenda de Carlos Arbeladez-10/09/2026 13:00-10/09/2026 14:00</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26">
         <v>4</v>
       </c>
@@ -9667,43 +9652,43 @@
         <v>Agenda de Juan Ortiz-06/10/2026 13:00-06/10/2026 15:00</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34"/>
       <c r="B13" s="35" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="36"/>
       <c r="B14" s="35" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="57"/>
       <c r="B15" s="35" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="37"/>
       <c r="B16" s="35" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="93"/>
       <c r="B17" s="35" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="46"/>
       <c r="B18" s="35" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="47"/>
       <c r="B19" s="35" t="s">
         <v>86</v>
@@ -9727,31 +9712,31 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
   <dimension ref="A1:U12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="42.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.33203125" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" customWidth="1"/>
-    <col min="6" max="6" width="25.44140625" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" customWidth="1"/>
-    <col min="11" max="11" width="20.33203125" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" customWidth="1"/>
-    <col min="13" max="13" width="26.6640625" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="29.6640625" customWidth="1"/>
+    <col min="2" max="2" width="42.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" customWidth="1"/>
+    <col min="13" max="13" width="26.7109375" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="29.7109375" customWidth="1"/>
     <col min="16" max="16" width="27" customWidth="1"/>
-    <col min="17" max="17" width="41.44140625" customWidth="1"/>
-    <col min="18" max="18" width="38.88671875" customWidth="1"/>
-    <col min="19" max="19" width="22.88671875" customWidth="1"/>
-    <col min="20" max="20" width="25.88671875" customWidth="1"/>
+    <col min="17" max="17" width="41.42578125" customWidth="1"/>
+    <col min="18" max="18" width="38.85546875" customWidth="1"/>
+    <col min="19" max="19" width="22.85546875" customWidth="1"/>
+    <col min="20" max="20" width="25.85546875" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -9759,7 +9744,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>28</v>
       </c>
@@ -9824,7 +9809,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>'M-Cita'!A3</f>
         <v>id</v>
@@ -9871,7 +9856,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="str">
         <f>'M-Cita'!B3</f>
         <v>cliente</v>
@@ -9883,7 +9868,7 @@
       <c r="C4" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="132" t="s">
+      <c r="D4" s="128" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="14" t="s">
@@ -9916,7 +9901,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="str">
         <f>'M-Cita'!C3</f>
         <v>agenda</v>
@@ -9928,7 +9913,7 @@
       <c r="C5" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="132" t="s">
+      <c r="D5" s="128" t="s">
         <v>13</v>
       </c>
       <c r="E5" s="14" t="s">
@@ -9961,7 +9946,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="str">
         <f>'M-Cita'!D3</f>
         <v>fechaHora</v>
@@ -10008,7 +9993,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="str">
         <f>'M-Cita'!E3</f>
         <v>fechaHoraFin</v>
@@ -10055,7 +10040,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="144" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="144" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="str">
         <f>'M-Cita'!F3</f>
         <v>estado</v>
@@ -10110,7 +10095,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -10133,7 +10118,7 @@
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
     </row>
-    <row r="10" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>62</v>
       </c>
@@ -10143,31 +10128,31 @@
       <c r="C10" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="131"/>
-      <c r="E10" s="131"/>
-      <c r="F10" s="131"/>
-      <c r="G10" s="131"/>
-      <c r="H10" s="131"/>
-      <c r="I10" s="131"/>
-      <c r="J10" s="131"/>
-      <c r="K10" s="131"/>
-      <c r="L10" s="131"/>
-      <c r="M10" s="131"/>
-      <c r="N10" s="131"/>
-      <c r="O10" s="131"/>
-      <c r="P10" s="131"/>
-      <c r="Q10" s="131"/>
-      <c r="R10" s="131"/>
-      <c r="S10" s="131"/>
-      <c r="T10" s="131"/>
-      <c r="U10" s="131"/>
-    </row>
-    <row r="11" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="127" t="str">
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="38"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="38"/>
+      <c r="O10" s="38"/>
+      <c r="P10" s="38"/>
+      <c r="Q10" s="38"/>
+      <c r="R10" s="38"/>
+      <c r="S10" s="38"/>
+      <c r="T10" s="38"/>
+      <c r="U10" s="38"/>
+    </row>
+    <row r="11" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="130" t="str">
         <f>'M-Cita'!G3</f>
         <v>Combinación única</v>
       </c>
-      <c r="B11" s="128" t="str">
+      <c r="B11" s="131" t="str">
         <f>'M-Cita'!G2</f>
         <v xml:space="preserve">
 Combinación única que indica que una cita no puede existir dentro de una agenda con la misma fecha y hora de inicio para la cita</v>
@@ -10195,9 +10180,9 @@
       <c r="T11" s="5"/>
       <c r="U11" s="5"/>
     </row>
-    <row r="12" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="127"/>
-      <c r="B12" s="127"/>
+    <row r="12" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="130"/>
+      <c r="B12" s="130"/>
       <c r="C12" s="39" t="str">
         <f>A6</f>
         <v>fechaHora</v>
@@ -10240,18 +10225,18 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="33.44140625" customWidth="1"/>
-    <col min="4" max="4" width="30.33203125" customWidth="1"/>
-    <col min="5" max="5" width="36.109375" customWidth="1"/>
-    <col min="6" max="6" width="57.6640625" customWidth="1"/>
-    <col min="7" max="7" width="49.33203125" customWidth="1"/>
+    <col min="3" max="3" width="33.42578125" customWidth="1"/>
+    <col min="4" max="4" width="30.28515625" customWidth="1"/>
+    <col min="5" max="5" width="36.140625" customWidth="1"/>
+    <col min="6" max="6" width="57.7109375" customWidth="1"/>
+    <col min="7" max="7" width="49.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="94" t="s">
         <v>1</v>
       </c>
@@ -10259,7 +10244,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="95" t="s">
         <v>65</v>
       </c>
@@ -10282,7 +10267,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="96" t="s">
         <v>67</v>
       </c>
@@ -10305,7 +10290,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -10331,7 +10316,7 @@
         <v>Juan  Gómez -Agenda de Juan García-31/08/2026/10:00-31/08/2026/10:45</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26">
         <v>2</v>
       </c>
@@ -10357,7 +10342,7 @@
         <v>Jose Miguel Ramirez Perez-Agenda de Juan Ortiz-10/03/2026/09:30-10/03/2026/10:20</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26">
         <v>3</v>
       </c>
@@ -10383,7 +10368,7 @@
         <v>Simon  Ochoa Ramirez-Agenda de Carlos Arbeladez-14/05/2026/13:00-14/05/2026/13:15</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26">
         <v>4</v>
       </c>
@@ -10409,7 +10394,7 @@
         <v>Alexis  Gallego -Agenda de Andres Ramirez-22/11/2025/13:00-22/11/2025/13:40</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26">
         <v>5</v>
       </c>
@@ -10435,7 +10420,7 @@
         <v>Alexis  Gallego -Agenda de Carlos Arbeladez-06/08/2026/18:00-06/08/2026/18:15</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26">
         <v>6</v>
       </c>
@@ -10461,7 +10446,7 @@
         <v>Juan  Gómez -Agenda de Juan Ortiz-01/09/2026/14:00-01/09/2026/14:10</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26">
         <v>7</v>
       </c>
@@ -10487,7 +10472,7 @@
         <v>Kevin Andrés Muñoz Salazar-Agenda de Juan García-01/06/2026/10:00-01/06/2026/10:45</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26">
         <v>8</v>
       </c>
@@ -10513,7 +10498,7 @@
         <v>Kevin Andrés Muñoz Salazar-Agenda de Juan Ortiz-16/06/2026/09:00-16/06/2026/09:10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="26">
         <v>9</v>
       </c>
@@ -10539,55 +10524,55 @@
         <v>Kevin Andrés Muñoz Salazar-Agenda de Carlos Arbeladez-02/07/2026/15:00-02/07/2026/15:15</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="35"/>
     </row>
-    <row r="15" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="35"/>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="35"/>
     </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="35"/>
     </row>
-    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="34"/>
       <c r="B18" s="35" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="36"/>
       <c r="B19" s="35" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="57"/>
       <c r="B20" s="35" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="125"/>
       <c r="B21" s="35" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="93"/>
       <c r="B22" s="35" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="46"/>
       <c r="B23" s="35" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="47"/>
       <c r="B24" s="35" t="s">
         <v>86</v>
@@ -10626,31 +10611,31 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
   <dimension ref="A1:U10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="33.33203125" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" customWidth="1"/>
-    <col min="6" max="6" width="25.44140625" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" customWidth="1"/>
-    <col min="11" max="11" width="20.33203125" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" customWidth="1"/>
-    <col min="13" max="13" width="26.6640625" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" customWidth="1"/>
+    <col min="13" max="13" width="26.7109375" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="29.7109375" customWidth="1"/>
     <col min="16" max="16" width="27" customWidth="1"/>
-    <col min="17" max="17" width="41.44140625" customWidth="1"/>
-    <col min="18" max="18" width="38.88671875" customWidth="1"/>
-    <col min="19" max="19" width="22.88671875" customWidth="1"/>
-    <col min="20" max="20" width="25.88671875" customWidth="1"/>
+    <col min="17" max="17" width="41.42578125" customWidth="1"/>
+    <col min="18" max="18" width="38.85546875" customWidth="1"/>
+    <col min="19" max="19" width="22.85546875" customWidth="1"/>
+    <col min="20" max="20" width="25.85546875" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -10658,7 +10643,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>28</v>
       </c>
@@ -10723,7 +10708,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>'M-CitaServicio'!A3</f>
         <v>id</v>
@@ -10770,7 +10755,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="str">
         <f>'M-CitaServicio'!B3</f>
         <v>cita</v>
@@ -10819,7 +10804,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="str">
         <f>'M-CitaServicio'!C3</f>
         <v>servicio</v>
@@ -10868,7 +10853,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="100.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="100.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="str">
         <f>'M-CitaServicio'!D3</f>
         <v>precioAlMomento</v>
@@ -10921,7 +10906,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
@@ -10944,7 +10929,7 @@
       <c r="T7" s="5"/>
       <c r="U7" s="5"/>
     </row>
-    <row r="8" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>62</v>
       </c>
@@ -10973,12 +10958,12 @@
       <c r="T8" s="50"/>
       <c r="U8" s="50"/>
     </row>
-    <row r="9" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="127" t="str">
+    <row r="9" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="130" t="str">
         <f>'M-CitaServicio'!E3</f>
         <v>Combinación única</v>
       </c>
-      <c r="B9" s="128" t="str">
+      <c r="B9" s="131" t="str">
         <f>'M-CitaServicio'!E2</f>
         <v>Combinación única que indica que un mismo servicio no puede repetirse dos veces dentro de la misma cita</v>
       </c>
@@ -11005,9 +10990,9 @@
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
     </row>
-    <row r="10" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="127"/>
-      <c r="B10" s="127"/>
+    <row r="10" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="130"/>
+      <c r="B10" s="130"/>
       <c r="C10" s="39" t="str">
         <f>A5</f>
         <v>servicio</v>
@@ -11048,16 +11033,16 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
   <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="49.6640625" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" customWidth="1"/>
-    <col min="4" max="4" width="46.6640625" customWidth="1"/>
-    <col min="5" max="5" width="66.6640625" customWidth="1"/>
+    <col min="2" max="2" width="49.7109375" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" customWidth="1"/>
+    <col min="4" max="4" width="46.7109375" customWidth="1"/>
+    <col min="5" max="5" width="66.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="94" t="s">
         <v>1</v>
       </c>
@@ -11065,7 +11050,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="95" t="s">
         <v>65</v>
       </c>
@@ -11082,7 +11067,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="103" t="s">
         <v>67</v>
       </c>
@@ -11099,7 +11084,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -11119,7 +11104,7 @@
         <v>Juan  Gómez -Agenda de Juan García-31/08/2026/10:00-31/08/2026/10:45-Motilada</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26">
         <v>2</v>
       </c>
@@ -11139,7 +11124,7 @@
         <v>Jose Miguel Ramirez Perez-Agenda de Juan Ortiz-10/03/2026/09:30-10/03/2026/10:20-Corte de barba</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26">
         <v>3</v>
       </c>
@@ -11159,7 +11144,7 @@
         <v>Jose Miguel Ramirez Perez-Agenda de Juan Ortiz-10/03/2026/09:30-10/03/2026/10:20-Motilada</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26">
         <v>4</v>
       </c>
@@ -11179,7 +11164,7 @@
         <v>Simon  Ochoa Ramirez-Agenda de Carlos Arbeladez-14/05/2026/13:00-14/05/2026/13:15-Perfilada de barba</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26">
         <v>5</v>
       </c>
@@ -11199,7 +11184,7 @@
         <v>Alexis  Gallego -Agenda de Andres Ramirez-22/11/2025/13:00-22/11/2025/13:40-Arreglo completo de barba con toalla caliente</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26">
         <v>6</v>
       </c>
@@ -11219,7 +11204,7 @@
         <v>Alexis  Gallego -Agenda de Carlos Arbeladez-06/08/2026/18:00-06/08/2026/18:15-Corte de barba</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="26">
         <v>7</v>
       </c>
@@ -11239,7 +11224,7 @@
         <v>Juan  Gómez -Agenda de Juan Ortiz-01/09/2026/14:00-01/09/2026/14:10-Corte de barba</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26">
         <v>8</v>
       </c>
@@ -11259,7 +11244,7 @@
         <v>Kevin Andrés Muñoz Salazar-Agenda de Juan García-01/06/2026/10:00-01/06/2026/10:45-Motilada</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="26">
         <v>9</v>
       </c>
@@ -11279,7 +11264,7 @@
         <v>Kevin Andrés Muñoz Salazar-Agenda de Juan Ortiz-16/06/2026/09:00-16/06/2026/09:10-Corte de barba</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26">
         <v>10</v>
       </c>
@@ -11299,31 +11284,31 @@
         <v>Kevin Andrés Muñoz Salazar-Agenda de Carlos Arbeladez-02/07/2026/15:00-02/07/2026/15:15-Perfilada de barba</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="105"/>
       <c r="B19" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="106"/>
       <c r="B20" s="35" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="107"/>
       <c r="B21" s="35" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="108"/>
       <c r="B22" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="109"/>
       <c r="B23" t="s">
         <v>86</v>
@@ -11356,31 +11341,31 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
   <dimension ref="A1:U11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="33.33203125" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" customWidth="1"/>
-    <col min="6" max="6" width="25.44140625" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" customWidth="1"/>
-    <col min="11" max="11" width="20.33203125" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" customWidth="1"/>
-    <col min="13" max="13" width="26.6640625" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" customWidth="1"/>
+    <col min="13" max="13" width="26.7109375" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="29.7109375" customWidth="1"/>
     <col min="16" max="16" width="27" customWidth="1"/>
-    <col min="17" max="17" width="41.44140625" customWidth="1"/>
-    <col min="18" max="18" width="38.88671875" customWidth="1"/>
-    <col min="19" max="19" width="22.88671875" customWidth="1"/>
-    <col min="20" max="20" width="25.88671875" customWidth="1"/>
+    <col min="17" max="17" width="41.42578125" customWidth="1"/>
+    <col min="18" max="18" width="38.85546875" customWidth="1"/>
+    <col min="19" max="19" width="22.85546875" customWidth="1"/>
+    <col min="20" max="20" width="25.85546875" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -11388,7 +11373,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>28</v>
       </c>
@@ -11453,7 +11438,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>'M-Multa'!A3</f>
         <v>id</v>
@@ -11500,7 +11485,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="str">
         <f>'M-Multa'!B3</f>
         <v>cliente</v>
@@ -11549,7 +11534,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="str">
         <f>'M-Multa'!C3</f>
         <v>cita</v>
@@ -11598,7 +11583,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="str">
         <f>'M-Multa'!D3</f>
         <v>monto</v>
@@ -11651,7 +11636,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="str">
         <f>'M-Multa'!E3</f>
         <v>tipo</v>
@@ -11704,7 +11689,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="str">
         <f>'M-Multa'!F3</f>
         <v>pagada</v>
@@ -11753,7 +11738,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -11776,7 +11761,7 @@
       <c r="T9" s="5"/>
       <c r="U9" s="5"/>
     </row>
-    <row r="10" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>62</v>
       </c>
@@ -11805,7 +11790,7 @@
       <c r="T10" s="50"/>
       <c r="U10" s="50"/>
     </row>
-    <row r="11" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="str">
         <f>'M-Multa'!G3</f>
         <v>Combinación única</v>
@@ -11850,18 +11835,18 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
   <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
-    <col min="3" max="3" width="50.44140625" customWidth="1"/>
-    <col min="4" max="4" width="34.6640625" customWidth="1"/>
-    <col min="5" max="5" width="29.109375" customWidth="1"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1"/>
-    <col min="7" max="7" width="49.33203125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="3" max="3" width="50.42578125" customWidth="1"/>
+    <col min="4" max="4" width="34.7109375" customWidth="1"/>
+    <col min="5" max="5" width="29.140625" customWidth="1"/>
+    <col min="6" max="6" width="31.28515625" customWidth="1"/>
+    <col min="7" max="7" width="49.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="94" t="s">
         <v>1</v>
       </c>
@@ -11869,7 +11854,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="95" t="s">
         <v>65</v>
       </c>
@@ -11892,7 +11877,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="96" t="s">
         <v>67</v>
       </c>
@@ -11915,7 +11900,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -11942,7 +11927,7 @@
         <v>Simon  Ochoa Ramirez-Agenda de Carlos Arbeladez-14/05/2026/13:00-14/05/2026/13:15</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26">
         <v>2</v>
       </c>
@@ -11969,7 +11954,7 @@
         <v>Alexis  Gallego -Agenda de Andres Ramirez-22/11/2025/13:00-22/11/2025/13:40</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26">
         <v>3</v>
       </c>
@@ -11996,7 +11981,7 @@
         <v>Kevin Andrés Muñoz Salazar-Agenda de Juan García-01/06/2026/10:00-01/06/2026/10:45</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26">
         <v>4</v>
       </c>
@@ -12023,7 +12008,7 @@
         <v>Kevin Andrés Muñoz Salazar-Agenda de Juan Ortiz-16/06/2026/09:00-16/06/2026/09:10</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26">
         <v>5</v>
       </c>
@@ -12050,37 +12035,37 @@
         <v>Kevin Andrés Muñoz Salazar-Agenda de Carlos Arbeladez-02/07/2026/15:00-02/07/2026/15:15</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="105"/>
       <c r="B14" s="35" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="113"/>
       <c r="B15" s="35" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="107"/>
       <c r="B16" s="35" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="114"/>
       <c r="B17" s="35" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="115"/>
       <c r="B18" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="116"/>
       <c r="B19" t="s">
         <v>86</v>
@@ -12105,31 +12090,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:U7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="33.33203125" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" customWidth="1"/>
-    <col min="6" max="6" width="25.44140625" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" customWidth="1"/>
-    <col min="11" max="11" width="20.33203125" customWidth="1"/>
-    <col min="12" max="12" width="28.109375" customWidth="1"/>
-    <col min="13" max="13" width="26.6640625" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" customWidth="1"/>
+    <col min="12" max="12" width="28.140625" customWidth="1"/>
+    <col min="13" max="13" width="26.7109375" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="29.7109375" customWidth="1"/>
     <col min="16" max="16" width="27" customWidth="1"/>
-    <col min="17" max="17" width="41.44140625" customWidth="1"/>
-    <col min="18" max="18" width="38.88671875" customWidth="1"/>
-    <col min="19" max="19" width="22.88671875" customWidth="1"/>
-    <col min="20" max="20" width="25.88671875" customWidth="1"/>
+    <col min="17" max="17" width="41.42578125" customWidth="1"/>
+    <col min="18" max="18" width="38.85546875" customWidth="1"/>
+    <col min="19" max="19" width="22.85546875" customWidth="1"/>
+    <col min="20" max="20" width="25.85546875" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -12137,7 +12122,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>28</v>
       </c>
@@ -12202,7 +12187,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>'M-Agenda'!A3</f>
         <v>id</v>
@@ -12249,7 +12234,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="str">
         <f>'M-Agenda'!B3</f>
         <v>nombre</v>
@@ -12300,7 +12285,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
       <c r="C5" s="16"/>
@@ -12323,7 +12308,7 @@
       <c r="T5" s="16"/>
       <c r="U5" s="16"/>
     </row>
-    <row r="6" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
         <v>62</v>
       </c>
@@ -12352,7 +12337,7 @@
       <c r="T6" s="18"/>
       <c r="U6" s="18"/>
     </row>
-    <row r="7" spans="1:21" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="54.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="str">
         <f>'M-Agenda'!C3</f>
         <v>Combinación única</v>
@@ -12397,14 +12382,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="48" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -12412,7 +12397,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="58.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
         <v>65</v>
       </c>
@@ -12423,7 +12408,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>67</v>
       </c>
@@ -12434,7 +12419,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -12446,7 +12431,7 @@
         <v>Agenda de Juan García</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26">
         <v>2</v>
       </c>
@@ -12458,7 +12443,7 @@
         <v>Agenda de Juan Ortiz</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26">
         <v>3</v>
       </c>
@@ -12470,7 +12455,7 @@
         <v>Agenda de Carlos Arbeladez</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26">
         <v>4</v>
       </c>
@@ -12482,7 +12467,7 @@
         <v>Agenda de Andres Ramirez</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26">
         <v>5</v>
       </c>
@@ -12494,27 +12479,27 @@
         <v>Agenda de Juan Carlos Zambrano</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="118"/>
       <c r="B13" s="35" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="119"/>
       <c r="B14" s="35" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="120"/>
       <c r="B15" s="35" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="121"/>
       <c r="B16" t="s">
         <v>86</v>
@@ -12533,31 +12518,31 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:U10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="33.33203125" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" customWidth="1"/>
-    <col min="6" max="6" width="25.44140625" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" customWidth="1"/>
-    <col min="11" max="11" width="20.33203125" customWidth="1"/>
-    <col min="12" max="12" width="28.109375" customWidth="1"/>
-    <col min="13" max="13" width="26.6640625" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" customWidth="1"/>
+    <col min="12" max="12" width="28.140625" customWidth="1"/>
+    <col min="13" max="13" width="26.7109375" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="29.7109375" customWidth="1"/>
     <col min="16" max="16" width="27" customWidth="1"/>
-    <col min="17" max="17" width="41.44140625" customWidth="1"/>
-    <col min="18" max="18" width="38.88671875" customWidth="1"/>
-    <col min="19" max="19" width="22.88671875" customWidth="1"/>
-    <col min="20" max="20" width="25.88671875" customWidth="1"/>
+    <col min="17" max="17" width="41.42578125" customWidth="1"/>
+    <col min="18" max="18" width="38.85546875" customWidth="1"/>
+    <col min="19" max="19" width="22.85546875" customWidth="1"/>
+    <col min="20" max="20" width="25.85546875" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -12565,7 +12550,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>28</v>
       </c>
@@ -12630,7 +12615,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>'M-Dueño'!A3</f>
         <v>id</v>
@@ -12677,7 +12662,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="105" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="105" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="str">
         <f>'M-Dueño'!B3</f>
         <v>correo</v>
@@ -12730,7 +12715,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="str">
         <f>'M-Dueño'!C3</f>
         <v>contraseña</v>
@@ -12783,7 +12768,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="str">
         <f>'M-Dueño'!D3</f>
         <v>nombre</v>
@@ -12834,7 +12819,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="16"/>
       <c r="B7" s="16"/>
       <c r="C7" s="16"/>
@@ -12857,7 +12842,7 @@
       <c r="T7" s="16"/>
       <c r="U7" s="16"/>
     </row>
-    <row r="8" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>62</v>
       </c>
@@ -12886,14 +12871,14 @@
       <c r="T8" s="18"/>
       <c r="U8" s="18"/>
     </row>
-    <row r="9" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="127" t="s">
+    <row r="9" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="130" t="s">
         <v>88</v>
       </c>
-      <c r="B9" s="128" t="s">
+      <c r="B9" s="131" t="s">
         <v>89</v>
       </c>
-      <c r="C9" s="129" t="str">
+      <c r="C9" s="132" t="str">
         <f>A4</f>
         <v>correo</v>
       </c>
@@ -12916,10 +12901,10 @@
       <c r="T9" s="16"/>
       <c r="U9" s="16"/>
     </row>
-    <row r="10" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="127"/>
-      <c r="B10" s="127"/>
-      <c r="C10" s="127"/>
+    <row r="10" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="130"/>
+      <c r="B10" s="130"/>
+      <c r="C10" s="130"/>
       <c r="D10" s="16"/>
       <c r="E10" s="16"/>
       <c r="F10" s="16"/>
@@ -12959,16 +12944,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:E12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.88671875" customWidth="1"/>
+    <col min="1" max="1" width="39.85546875" customWidth="1"/>
     <col min="2" max="2" width="49" customWidth="1"/>
-    <col min="3" max="3" width="69.33203125" customWidth="1"/>
-    <col min="4" max="4" width="45.6640625" customWidth="1"/>
-    <col min="5" max="5" width="35.109375" customWidth="1"/>
+    <col min="3" max="3" width="69.28515625" customWidth="1"/>
+    <col min="4" max="4" width="45.7109375" customWidth="1"/>
+    <col min="5" max="5" width="35.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -12976,7 +12961,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
         <v>65</v>
       </c>
@@ -12991,7 +12976,7 @@
       </c>
       <c r="E2" s="30"/>
     </row>
-    <row r="3" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>67</v>
       </c>
@@ -13006,7 +12991,7 @@
       </c>
       <c r="E3" s="30"/>
     </row>
-    <row r="4" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -13021,19 +13006,19 @@
       </c>
       <c r="E4" s="30"/>
     </row>
-    <row r="10" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="34"/>
       <c r="B10" s="35" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="36"/>
       <c r="B11" s="35" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="37"/>
       <c r="B12" s="35" t="s">
         <v>82</v>
@@ -13053,31 +13038,31 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:U20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="33.33203125" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" customWidth="1"/>
-    <col min="6" max="6" width="25.44140625" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" customWidth="1"/>
-    <col min="11" max="11" width="20.33203125" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" customWidth="1"/>
-    <col min="13" max="13" width="26.6640625" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" customWidth="1"/>
+    <col min="13" max="13" width="26.7109375" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="29.7109375" customWidth="1"/>
     <col min="16" max="16" width="27" customWidth="1"/>
-    <col min="17" max="17" width="41.44140625" customWidth="1"/>
-    <col min="18" max="18" width="38.88671875" customWidth="1"/>
-    <col min="19" max="19" width="22.88671875" customWidth="1"/>
-    <col min="20" max="20" width="25.88671875" customWidth="1"/>
+    <col min="17" max="17" width="41.42578125" customWidth="1"/>
+    <col min="18" max="18" width="38.85546875" customWidth="1"/>
+    <col min="19" max="19" width="22.85546875" customWidth="1"/>
+    <col min="20" max="20" width="25.85546875" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -13085,7 +13070,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>28</v>
       </c>
@@ -13150,7 +13135,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>'M-Barbero'!A3</f>
         <v>id</v>
@@ -13197,7 +13182,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="str">
         <f>'M-Barbero'!B3</f>
         <v>primerNombre</v>
@@ -13248,7 +13233,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="str">
         <f>'M-Barbero'!C3</f>
         <v>segundoNombre</v>
@@ -13299,7 +13284,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="str">
         <f>'M-Barbero'!D3</f>
         <v>primerApellido</v>
@@ -13350,7 +13335,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="str">
         <f>'M-Barbero'!E3</f>
         <v>segundoApellido</v>
@@ -13401,7 +13386,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="str">
         <f>'M-Barbero'!F3</f>
         <v>prefijo</v>
@@ -13456,7 +13441,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="str">
         <f>'M-Barbero'!G3</f>
         <v>celular</v>
@@ -13511,7 +13496,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="129" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="129" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="str">
         <f>'M-Barbero'!H3</f>
         <v>correo</v>
@@ -13564,7 +13549,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="str">
         <f>'M-Barbero'!I3</f>
         <v>contraseña</v>
@@ -13617,7 +13602,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="str">
         <f>'M-Barbero'!J3</f>
         <v>vigente</v>
@@ -13666,7 +13651,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -13689,7 +13674,7 @@
       <c r="T13" s="5"/>
       <c r="U13" s="5"/>
     </row>
-    <row r="14" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>62</v>
       </c>
@@ -13718,12 +13703,12 @@
       <c r="T14" s="38"/>
       <c r="U14" s="38"/>
     </row>
-    <row r="15" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="127" t="str">
+    <row r="15" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="130" t="str">
         <f>'M-Barbero'!K3</f>
         <v xml:space="preserve">Combinación única </v>
       </c>
-      <c r="B15" s="128" t="str">
+      <c r="B15" s="131" t="str">
         <f>'M-Barbero'!K2</f>
         <v>Combinacion única que indica que no puede existir más de un barbero con el mismo nombre, apellidos, prefijo de celular y número de celular</v>
       </c>
@@ -13750,9 +13735,9 @@
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
     </row>
-    <row r="16" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="127"/>
-      <c r="B16" s="127"/>
+    <row r="16" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="130"/>
+      <c r="B16" s="130"/>
       <c r="C16" s="39" t="str">
         <f t="shared" si="0"/>
         <v>segundoNombre</v>
@@ -13776,9 +13761,9 @@
       <c r="T16" s="5"/>
       <c r="U16" s="5"/>
     </row>
-    <row r="17" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="127"/>
-      <c r="B17" s="127"/>
+    <row r="17" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="130"/>
+      <c r="B17" s="130"/>
       <c r="C17" s="39" t="str">
         <f t="shared" si="0"/>
         <v>primerApellido</v>
@@ -13802,9 +13787,9 @@
       <c r="T17" s="5"/>
       <c r="U17" s="5"/>
     </row>
-    <row r="18" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="127"/>
-      <c r="B18" s="127"/>
+    <row r="18" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="130"/>
+      <c r="B18" s="130"/>
       <c r="C18" s="39" t="str">
         <f t="shared" si="0"/>
         <v>segundoApellido</v>
@@ -13828,9 +13813,9 @@
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
     </row>
-    <row r="19" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="127"/>
-      <c r="B19" s="127"/>
+    <row r="19" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="130"/>
+      <c r="B19" s="130"/>
       <c r="C19" s="39" t="str">
         <f t="shared" si="0"/>
         <v>prefijo</v>
@@ -13854,9 +13839,9 @@
       <c r="T19" s="5"/>
       <c r="U19" s="5"/>
     </row>
-    <row r="20" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="127"/>
-      <c r="B20" s="127"/>
+    <row r="20" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="130"/>
+      <c r="B20" s="130"/>
       <c r="C20" s="39" t="str">
         <f t="shared" si="0"/>
         <v>celular</v>
@@ -13897,22 +13882,22 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:K18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="26.109375" customWidth="1"/>
-    <col min="3" max="3" width="23.33203125" customWidth="1"/>
-    <col min="4" max="4" width="24.109375" customWidth="1"/>
-    <col min="5" max="5" width="25.5546875" customWidth="1"/>
-    <col min="6" max="6" width="23.33203125" customWidth="1"/>
-    <col min="7" max="7" width="19.33203125" customWidth="1"/>
-    <col min="8" max="8" width="33.77734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="68.5546875" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+    <col min="4" max="4" width="24.140625" customWidth="1"/>
+    <col min="5" max="5" width="25.5703125" customWidth="1"/>
+    <col min="6" max="6" width="23.28515625" customWidth="1"/>
+    <col min="7" max="7" width="19.28515625" customWidth="1"/>
+    <col min="8" max="8" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="68.5703125" customWidth="1"/>
     <col min="10" max="10" width="32" customWidth="1"/>
-    <col min="11" max="11" width="41.5546875" customWidth="1"/>
+    <col min="11" max="11" width="41.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -13924,7 +13909,7 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="40" t="s">
         <v>65</v>
       </c>
@@ -13959,7 +13944,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>67</v>
       </c>
@@ -13994,7 +13979,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26">
         <v>1</v>
       </c>
@@ -14030,7 +14015,7 @@
         <v>Juan-Fernando-García-Lopez-+57-3245627890</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="26">
         <v>2</v>
       </c>
@@ -14066,7 +14051,7 @@
         <v>Juan-David-Ortiz-Sanchez-+57-3124518923</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="26">
         <v>3</v>
       </c>
@@ -14098,7 +14083,7 @@
         <v>Carlos--Arbeladez--+57-3214533321</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="26">
         <v>4</v>
       </c>
@@ -14132,7 +14117,7 @@
         <v>Andres--Ramirez-Patiño-+91-9876543210</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26">
         <v>5</v>
       </c>
@@ -14168,31 +14153,31 @@
         <v>Juan-Carlos-Zambrano-Perez-+593-998765432</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="34"/>
       <c r="B14" s="35" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="36"/>
       <c r="B15" s="35" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="37"/>
       <c r="B16" s="35" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="46"/>
       <c r="B17" s="35" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="47"/>
       <c r="B18" s="35" t="s">
         <v>86</v>
@@ -14216,31 +14201,31 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:U19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="33.33203125" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" customWidth="1"/>
-    <col min="6" max="6" width="25.44140625" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.6640625" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" customWidth="1"/>
-    <col min="11" max="11" width="20.33203125" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" customWidth="1"/>
-    <col min="13" max="13" width="26.6640625" customWidth="1"/>
-    <col min="14" max="14" width="14.33203125" customWidth="1"/>
-    <col min="15" max="15" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.42578125" customWidth="1"/>
+    <col min="7" max="7" width="25.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="21.85546875" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" customWidth="1"/>
+    <col min="12" max="12" width="17.7109375" customWidth="1"/>
+    <col min="13" max="13" width="26.7109375" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" customWidth="1"/>
+    <col min="15" max="15" width="29.7109375" customWidth="1"/>
     <col min="16" max="16" width="27" customWidth="1"/>
-    <col min="17" max="17" width="41.44140625" customWidth="1"/>
-    <col min="18" max="18" width="38.88671875" customWidth="1"/>
-    <col min="19" max="19" width="22.88671875" customWidth="1"/>
-    <col min="20" max="20" width="25.88671875" customWidth="1"/>
+    <col min="17" max="17" width="41.42578125" customWidth="1"/>
+    <col min="18" max="18" width="38.85546875" customWidth="1"/>
+    <col min="19" max="19" width="22.85546875" customWidth="1"/>
+    <col min="20" max="20" width="25.85546875" customWidth="1"/>
     <col min="21" max="21" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>1</v>
       </c>
@@ -14248,7 +14233,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
         <v>28</v>
       </c>
@@ -14313,7 +14298,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="str">
         <f>'M-Cliente'!A3</f>
         <v>id</v>
@@ -14360,7 +14345,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="str">
         <f>'M-Cliente'!B3</f>
         <v>primerNombre</v>
@@ -14411,7 +14396,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="str">
         <f>'M-Cliente'!C3</f>
         <v>segundoNombre</v>
@@ -14462,7 +14447,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="str">
         <f>'M-Cliente'!D3</f>
         <v>primerApellido</v>
@@ -14513,7 +14498,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="str">
         <f>'M-Cliente'!E3</f>
         <v>segundoApellido</v>
@@ -14564,7 +14549,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="str">
         <f>'M-Cliente'!F3</f>
         <v>prefijoCelular</v>
@@ -14619,7 +14604,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" ht="57" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="str">
         <f>'M-Cliente'!G3</f>
         <v>celular</v>
@@ -14672,7 +14657,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="str">
         <f>'M-Cliente'!H3</f>
         <v>multasSinPagar</v>
@@ -14717,7 +14702,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="str">
         <f>'M-Cliente'!I3</f>
         <v>estaVetado</v>
@@ -14762,7 +14747,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -14785,7 +14770,7 @@
       <c r="T12" s="5"/>
       <c r="U12" s="5"/>
     </row>
-    <row r="13" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>62</v>
       </c>
@@ -14814,12 +14799,12 @@
       <c r="T13" s="38"/>
       <c r="U13" s="38"/>
     </row>
-    <row r="14" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="127" t="str">
+    <row r="14" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="130" t="str">
         <f>'M-Cliente'!J3</f>
         <v>Combinación única</v>
       </c>
-      <c r="B14" s="128" t="str">
+      <c r="B14" s="131" t="str">
         <f>'M-Cliente'!J2</f>
         <v>Combinacion única que indica que no puede existir más de un cliente con un mismo nombre, apellidos, prefijo de celular y número de celular</v>
       </c>
@@ -14846,9 +14831,9 @@
       <c r="T14" s="5"/>
       <c r="U14" s="5"/>
     </row>
-    <row r="15" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="127"/>
-      <c r="B15" s="127"/>
+    <row r="15" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="130"/>
+      <c r="B15" s="130"/>
       <c r="C15" s="39" t="str">
         <f t="shared" si="0"/>
         <v>segundoNombre</v>
@@ -14872,9 +14857,9 @@
       <c r="T15" s="5"/>
       <c r="U15" s="5"/>
     </row>
-    <row r="16" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="127"/>
-      <c r="B16" s="127"/>
+    <row r="16" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="130"/>
+      <c r="B16" s="130"/>
       <c r="C16" s="39" t="str">
         <f t="shared" si="0"/>
         <v>primerApellido</v>
@@ -14898,9 +14883,9 @@
       <c r="T16" s="5"/>
       <c r="U16" s="5"/>
     </row>
-    <row r="17" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="127"/>
-      <c r="B17" s="127"/>
+    <row r="17" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="130"/>
+      <c r="B17" s="130"/>
       <c r="C17" s="39" t="str">
         <f t="shared" si="0"/>
         <v>segundoApellido</v>
@@ -14924,9 +14909,9 @@
       <c r="T17" s="5"/>
       <c r="U17" s="5"/>
     </row>
-    <row r="18" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="127"/>
-      <c r="B18" s="127"/>
+    <row r="18" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="130"/>
+      <c r="B18" s="130"/>
       <c r="C18" s="39" t="str">
         <f t="shared" si="0"/>
         <v>prefijoCelular</v>
@@ -14950,9 +14935,9 @@
       <c r="T18" s="5"/>
       <c r="U18" s="5"/>
     </row>
-    <row r="19" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="127"/>
-      <c r="B19" s="127"/>
+    <row r="19" spans="1:21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="130"/>
+      <c r="B19" s="130"/>
       <c r="C19" s="39" t="str">
         <f t="shared" si="0"/>
         <v>celular</v>
